--- a/registration_forms/032_ai_project_beta_test_registration--registration_forms.xlsx
+++ b/registration_forms/032_ai_project_beta_test_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -990,12 +990,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'windows_10/11',_'value':_'windows'}</t>
+          <t>windows_10/11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Windows 10/11', 'value': 'windows'}</t>
+          <t>Windows 10/11</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'macos',_'value':_'macos'}</t>
+          <t>macos</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'macOS', 'value': 'macos'}</t>
+          <t>macOS</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'linux_(ubuntu/debian/etc.)',_'value':_'linux'}</t>
+          <t>linux_(ubuntu/debian/etc.)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Linux (Ubuntu/Debian/etc.)', 'value': 'linux'}</t>
+          <t>Linux (Ubuntu/Debian/etc.)</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'ios_(iphone/ipad)',_'value':_'ios'}</t>
+          <t>ios_(iphone/ipad)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'iOS (iPhone/iPad)', 'value': 'ios'}</t>
+          <t>iOS (iPhone/iPad)</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'android',_'value':_'android'}</t>
+          <t>android</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Android', 'value': 'android'}</t>
+          <t>Android</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'google_chrome',_'value':_'chrome'}</t>
+          <t>google_chrome</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Google Chrome', 'value': 'chrome'}</t>
+          <t>Google Chrome</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'mozilla_firefox',_'value':_'firefox'}</t>
+          <t>mozilla_firefox</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Mozilla Firefox', 'value': 'firefox'}</t>
+          <t>Mozilla Firefox</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'safari',_'value':_'safari'}</t>
+          <t>safari</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Safari', 'value': 'safari'}</t>
+          <t>Safari</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'microsoft_edge',_'value':_'edge'}</t>
+          <t>microsoft_edge</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Microsoft Edge', 'value': 'edge'}</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'brave_/_other',_'value':_'other'}</t>
+          <t>brave_/_other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Brave / Other', 'value': 'other'}</t>
+          <t>Brave / Other</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_hours',_'value':_'1-2'}</t>
+          <t>1-2_hours</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': '1-2 hours', 'value': '1-2'}</t>
+          <t>1-2 hours</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'3-5_hours',_'value':_'3-5'}</t>
+          <t>3-5_hours</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '3-5 hours', 'value': '3-5'}</t>
+          <t>3-5 hours</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'5-10_hours',_'value':_'5-10'}</t>
+          <t>5-10_hours</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '5-10 hours', 'value': '5-10'}</t>
+          <t>5-10 hours</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'10+_hours',_'value':_'10plus'}</t>
+          <t>10+_hours</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '10+ hours', 'value': '10plus'}</t>
+          <t>10+ hours</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'natural_language_processing_(nlp)',_'value':_'nlp'}</t>
+          <t>natural_language_processing_(nlp)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Natural Language Processing (NLP)', 'value': 'nlp'}</t>
+          <t>Natural Language Processing (NLP)</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'image_generation_/_vision',_'value':_'vision'}</t>
+          <t>image_generation_/_vision</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Image Generation / Vision', 'value': 'vision'}</t>
+          <t>Image Generation / Vision</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'api_integrations',_'value':_'api'}</t>
+          <t>api_integrations</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'API Integrations', 'value': 'api'}</t>
+          <t>API Integrations</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'performance_/_speed_benchmarking',_'value':_'performance'}</t>
+          <t>performance_/_speed_benchmarking</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Performance / Speed Benchmarking', 'value': 'performance'}</t>
+          <t>Performance / Speed Benchmarking</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'user_interface_(ux)_&amp;_design',_'value':_'ux'}</t>
+          <t>user_interface_(ux)_&amp;_design</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'User Interface (UX) &amp; Design', 'value': 'ux'}</t>
+          <t>User Interface (UX) &amp; Design</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'dedicated_discord_server',_'value':_'discord'}</t>
+          <t>dedicated_discord_server</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Dedicated Discord Server', 'value': 'discord'}</t>
+          <t>Dedicated Discord Server</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'email_/_support_tickets',_'value':_'email'}</t>
+          <t>email_/_support_tickets</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Email / Support Tickets', 'value': 'email'}</t>
+          <t>Email / Support Tickets</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'in-app_feedback_tool',_'value':_'in_app'}</t>
+          <t>in-app_feedback_tool</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'In-app Feedback Tool', 'value': 'in_app'}</t>
+          <t>In-app Feedback Tool</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree_to_keep_all_beta_features_and_screenshots_confidential.',_'value':_'agreed'}</t>
+          <t>i_agree_to_keep_all_beta_features_and_screenshots_confidential.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'I agree to keep all beta features and screenshots confidential.', 'value': 'agreed'}</t>
+          <t>I agree to keep all beta features and screenshots confidential.</t>
         </is>
       </c>
     </row>
